--- a/样品寄送模版.xlsx
+++ b/样品寄送模版.xlsx
@@ -501,6 +501,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF666666"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
       <t>白丝绒绵绵酪乳</t>
     </r>
     <r>
@@ -1248,7 +1254,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1320,9 +1326,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -1721,77 +1724,77 @@
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="1:16">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="26" t="s">
+      <c r="L1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="26" t="s">
+      <c r="M1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="26" t="s">
+      <c r="N1" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="26" t="s">
+      <c r="O1" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="26" t="s">
+      <c r="P1" s="25" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" s="25" customFormat="1" ht="24.95" customHeight="1" spans="1:16">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29">
+    <row r="2" s="24" customFormat="1" ht="24.95" customHeight="1" spans="1:16">
+      <c r="A2" s="27"/>
+      <c r="B2" s="28">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
-      </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="31" t="s">
+        <v>46315</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
       <c r="N2" s="7"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="33"/>
+      <c r="P2" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2504,7 +2507,7 @@
       <c r="A87" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="B87" s="24">
+      <c r="B87" s="7">
         <v>6978836201332</v>
       </c>
     </row>
